--- a/templates/Sport_Conversion_Google_-_Template.xlsx
+++ b/templates/Sport_Conversion_Google_-_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Omri PPC\SportBetting Google\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Omri PPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94CDFAE0-592B-4A9D-A306-A1D407A6703A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CD939A-7BE7-479F-A8C1-BBA16174C723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="conversion-import-template" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="35">
   <si>
     <t>Parameters:TimeZone=America/New_York;</t>
   </si>
@@ -119,6 +119,24 @@
   </si>
   <si>
     <t>offline - unibet</t>
+  </si>
+  <si>
+    <t>offline - casimba</t>
+  </si>
+  <si>
+    <t>offline - grandivy</t>
+  </si>
+  <si>
+    <t>offline - bet mgm</t>
+  </si>
+  <si>
+    <t>offline - betano</t>
+  </si>
+  <si>
+    <t>offline - dragonbet</t>
+  </si>
+  <si>
+    <t>offline - betway</t>
   </si>
 </sst>
 </file>
@@ -501,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="107.140625" customWidth="1"/>
@@ -541,7 +559,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="1">
-        <v>46024.996527777781</v>
+        <v>46171.996527777781</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -558,7 +576,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="1">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" t="s">
@@ -573,7 +591,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="1">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" t="s">
@@ -588,7 +606,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" t="s">
@@ -603,7 +621,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -617,7 +635,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -631,7 +649,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -645,7 +663,7 @@
         <v>13</v>
       </c>
       <c r="C11" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -659,7 +677,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -673,7 +691,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -687,7 +705,7 @@
         <v>18</v>
       </c>
       <c r="C14" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -701,7 +719,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
@@ -715,7 +733,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -729,7 +747,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
@@ -743,7 +761,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E18" t="s">
         <v>6</v>
@@ -757,7 +775,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
@@ -771,7 +789,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
@@ -785,7 +803,7 @@
         <v>25</v>
       </c>
       <c r="C21" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E21" t="s">
         <v>6</v>
@@ -799,7 +817,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
@@ -813,7 +831,7 @@
         <v>27</v>
       </c>
       <c r="C23" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
@@ -827,9 +845,93 @@
         <v>28</v>
       </c>
       <c r="C24" s="3">
-        <v>46024.998611111114</v>
+        <v>46171.998611111114</v>
       </c>
       <c r="E24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="3">
+        <v>46171.998611111114</v>
+      </c>
+      <c r="E25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="3">
+        <v>46171.998611111114</v>
+      </c>
+      <c r="E26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="3">
+        <v>46171.998611111114</v>
+      </c>
+      <c r="E27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="3">
+        <v>46171.998611111114</v>
+      </c>
+      <c r="E28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="3">
+        <v>46171.998611111114</v>
+      </c>
+      <c r="E29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="3">
+        <v>46171.998611111114</v>
+      </c>
+      <c r="E30" t="s">
         <v>6</v>
       </c>
     </row>
@@ -840,21 +942,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C40BB463539D3240B71C243B80C06056" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ca672511a255fc879d499e7cfd3414b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3d935cd2-bfa1-4639-8afd-89415ae12733" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e1e738df3222ccc84a773b64d405138" ns3:_="">
     <xsd:import namespace="3d935cd2-bfa1-4639-8afd-89415ae12733"/>
@@ -992,31 +1079,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7960F92F-7BB9-4753-88BC-3C3090539E7F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="3d935cd2-bfa1-4639-8afd-89415ae12733"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A61F8312-CA35-4899-8C65-EC7A689F2EF3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E0D8AB1-343D-48A5-8ED3-1ACDBEBB89D2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1032,4 +1110,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A61F8312-CA35-4899-8C65-EC7A689F2EF3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7960F92F-7BB9-4753-88BC-3C3090539E7F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3d935cd2-bfa1-4639-8afd-89415ae12733"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>